--- a/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_CB_VALL_D’EN_BAS_1_vs_CB_ADEPAF_TXOTS_50-62_analysis.xlsx
+++ b/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_CB_VALL_D’EN_BAS_1_vs_CB_ADEPAF_TXOTS_50-62_analysis.xlsx
@@ -1120,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>17</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>25</v>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0</v>
